--- a/Java基礎④-1_制御構文(if,switch)_演習問題.xlsx
+++ b/Java基礎④-1_制御構文(if,switch)_演習問題.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\村石 莉彩\Desktop\研修資料\10_Java\02_演習\01_基礎\問題\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pleiades-2024-12-java-win-64bit-jre_20250120\workspace\Java\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{101F12ED-72EC-4852-8F1E-46B2314FD34C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{ADB990B3-84E5-49CA-A23B-2C2542E0E78B}"/>
+    <workbookView xWindow="32655" yWindow="1830" windowWidth="17280" windowHeight="12390" activeTab="1" xr2:uid="{ADB990B3-84E5-49CA-A23B-2C2542E0E78B}"/>
   </bookViews>
   <sheets>
     <sheet name="第7章 制御構文（if文）" sheetId="2" r:id="rId1"/>
@@ -1161,6 +1161,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4f770298-b31c-4238-a90d-db1340869ae4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4ebca473-6c88-4eeb-9b46-7f2093239612" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100D00E93C39DF401468E770D4882DF02E4" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="96f527420be350019f68a523211badd0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4f770298-b31c-4238-a90d-db1340869ae4" xmlns:ns3="4ebca473-6c88-4eeb-9b46-7f2093239612" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="43e7199c2f8c1b8a43238954ae45261b" ns2:_="" ns3:_="">
     <xsd:import namespace="4f770298-b31c-4238-a90d-db1340869ae4"/>
@@ -1367,17 +1378,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4f770298-b31c-4238-a90d-db1340869ae4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4ebca473-6c88-4eeb-9b46-7f2093239612" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1388,6 +1388,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20C0C968-26DF-4A5E-9CB8-AB04E38C1611}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4f770298-b31c-4238-a90d-db1340869ae4"/>
+    <ds:schemaRef ds:uri="4ebca473-6c88-4eeb-9b46-7f2093239612"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A62A6DB-4A4F-4560-8A51-204E8EA06CC8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1406,17 +1417,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20C0C968-26DF-4A5E-9CB8-AB04E38C1611}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4f770298-b31c-4238-a90d-db1340869ae4"/>
-    <ds:schemaRef ds:uri="4ebca473-6c88-4eeb-9b46-7f2093239612"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD9F6378-B7CA-4063-BE72-365E29E465CD}">
   <ds:schemaRefs>
